--- a/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>As HealthcareService HealthCare Activity Profile</t>
+    <t>AS HealthcareService HealthCare Activity Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de la ressource HealthcareService dans le contexte de l'Annuaire Santé pour décrire les activités sanitaires rattachées à un établissement FINESS.</t>
+    <t>Profil créé à partir de HealthcareService dans le contexte de l'Annuaire Santé pour décrire les activités sanitaires rattachées à un établissement FINESS.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -456,7 +456,8 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les types d’activités sanitaires des établissements FINESS.</t>
   </si>
   <si>
-    <t>Synonyme MOS : activite ; la liste des activités de soins soumises à autorisation est fixée par décret en Conseil d'Etat (article L.6122-25 du CSP).</t>
+    <t>Synonyme : activite 
+ la liste des activités de soins soumises à autorisation est fixée par décret en Conseil d'Etat (article L.6122-25 du CSP).</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-healthcareservice-authorization-date</t>
@@ -523,7 +524,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour en compte de l'indicateur de suppression de l'autorisation de l'activité de soins.</t>
   </si>
   <si>
-    <t>Synonyme MOS : suppressionAutorisation ; donnée propre à FINESS</t>
+    <t>Synonyme : suppressionAutorisation ; donnée propre à FINESS</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-healthcareservice-date-update-activity</t>
@@ -542,7 +543,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la date  de mise à  jour des données de l'activité de soins.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateMajAutorisation</t>
+    <t>Synonyme : dateMajAutorisation</t>
   </si>
   <si>
     <t>HealthcareService.modifierExtension</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
